--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_beverage_soft.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0389</v>
+        <v>-0.0243</v>
       </c>
       <c r="G2">
-        <v>-0.05784431137724551</v>
+        <v>-0.24456</v>
       </c>
       <c r="H2">
-        <v>-0.06167664670658683</v>
+        <v>-0.2472</v>
       </c>
       <c r="I2">
-        <v>-0.188622754491018</v>
+        <v>-0.1224</v>
       </c>
       <c r="J2">
-        <v>-0.188622754491018</v>
+        <v>-0.1224</v>
       </c>
       <c r="K2">
-        <v>-3.07</v>
+        <v>-0.92</v>
       </c>
       <c r="L2">
-        <v>-0.1838323353293413</v>
+        <v>-0.0736</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.32</v>
+        <v>7.63</v>
       </c>
       <c r="V2">
-        <v>0.1062409288824383</v>
+        <v>0.1640860215053764</v>
       </c>
       <c r="W2">
-        <v>-0.4360795454545454</v>
+        <v>-0.07540983606557378</v>
       </c>
       <c r="X2">
-        <v>0.05477406960004411</v>
+        <v>0.1017454751891429</v>
       </c>
       <c r="Y2">
-        <v>-0.4908536150545895</v>
+        <v>-0.1771553112547167</v>
       </c>
       <c r="Z2">
-        <v>3.782559456398641</v>
+        <v>1.414027149321267</v>
       </c>
       <c r="AA2">
-        <v>-0.7134767836919592</v>
+        <v>-0.1730769230769231</v>
       </c>
       <c r="AB2">
-        <v>0.05359644393398203</v>
+        <v>0.09697737829662524</v>
       </c>
       <c r="AC2">
-        <v>-0.7670732276259412</v>
+        <v>-0.2700543013735483</v>
       </c>
       <c r="AD2">
-        <v>3.96</v>
+        <v>6.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.96</v>
+        <v>6.4</v>
       </c>
       <c r="AG2">
-        <v>-3.36</v>
+        <v>-1.23</v>
       </c>
       <c r="AH2">
-        <v>0.0543508097721658</v>
+        <v>0.1209829867674858</v>
       </c>
       <c r="AI2">
-        <v>0.2110874200426439</v>
+        <v>0.3516483516483516</v>
       </c>
       <c r="AJ2">
-        <v>-0.05126640219713152</v>
+        <v>-0.02717031146454605</v>
       </c>
       <c r="AK2">
-        <v>-0.2937062937062937</v>
+        <v>-0.1163670766319772</v>
       </c>
       <c r="AL2">
-        <v>0.08500000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="AM2">
-        <v>0.06900000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="AN2">
-        <v>-1.429602888086642</v>
+        <v>-9.155937052932762</v>
       </c>
       <c r="AO2">
-        <v>-37.05882352941176</v>
+        <v>-13.78378378378378</v>
       </c>
       <c r="AP2">
-        <v>1.212996389891697</v>
+        <v>1.759656652360514</v>
       </c>
       <c r="AQ2">
-        <v>-45.65217391304347</v>
+        <v>-15.14851485148515</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0389</v>
+        <v>-0.0243</v>
       </c>
       <c r="G3">
-        <v>-0.05784431137724551</v>
+        <v>-0.24456</v>
       </c>
       <c r="H3">
-        <v>-0.06167664670658683</v>
+        <v>-0.2472</v>
       </c>
       <c r="I3">
-        <v>-0.188622754491018</v>
+        <v>-0.1224</v>
       </c>
       <c r="J3">
-        <v>-0.188622754491018</v>
+        <v>-0.1224</v>
       </c>
       <c r="K3">
-        <v>-3.07</v>
+        <v>-0.92</v>
       </c>
       <c r="L3">
-        <v>-0.1838323353293413</v>
+        <v>-0.0736</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.32</v>
+        <v>7.63</v>
       </c>
       <c r="V3">
-        <v>0.1062409288824383</v>
+        <v>0.1640860215053764</v>
       </c>
       <c r="W3">
-        <v>-0.4360795454545454</v>
+        <v>-0.07540983606557378</v>
       </c>
       <c r="X3">
-        <v>0.05477406960004411</v>
+        <v>0.1017454751891429</v>
       </c>
       <c r="Y3">
-        <v>-0.4908536150545895</v>
+        <v>-0.1771553112547167</v>
       </c>
       <c r="Z3">
-        <v>3.782559456398641</v>
+        <v>1.414027149321267</v>
       </c>
       <c r="AA3">
-        <v>-0.7134767836919592</v>
+        <v>-0.1730769230769231</v>
       </c>
       <c r="AB3">
-        <v>0.05359644393398203</v>
+        <v>0.09697737829662524</v>
       </c>
       <c r="AC3">
-        <v>-0.7670732276259412</v>
+        <v>-0.2700543013735483</v>
       </c>
       <c r="AD3">
-        <v>3.96</v>
+        <v>6.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.96</v>
+        <v>6.4</v>
       </c>
       <c r="AG3">
-        <v>-3.36</v>
+        <v>-1.23</v>
       </c>
       <c r="AH3">
-        <v>0.0543508097721658</v>
+        <v>0.1209829867674858</v>
       </c>
       <c r="AI3">
-        <v>0.2110874200426439</v>
+        <v>0.3516483516483516</v>
       </c>
       <c r="AJ3">
-        <v>-0.05126640219713152</v>
+        <v>-0.02717031146454605</v>
       </c>
       <c r="AK3">
-        <v>-0.2937062937062937</v>
+        <v>-0.1163670766319772</v>
       </c>
       <c r="AL3">
-        <v>0.08500000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="AM3">
-        <v>0.06900000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="AN3">
-        <v>-1.429602888086642</v>
+        <v>-9.155937052932762</v>
       </c>
       <c r="AO3">
-        <v>-37.05882352941176</v>
+        <v>-13.78378378378378</v>
       </c>
       <c r="AP3">
-        <v>1.212996389891697</v>
+        <v>1.759656652360514</v>
       </c>
       <c r="AQ3">
-        <v>-45.65217391304347</v>
+        <v>-15.14851485148515</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_beverage_soft.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0243</v>
+        <v>-0.0309</v>
       </c>
       <c r="G2">
-        <v>-0.24456</v>
+        <v>-0.0146875</v>
       </c>
       <c r="H2">
-        <v>-0.2472</v>
+        <v>-0.016015625</v>
       </c>
       <c r="I2">
-        <v>-0.1224</v>
+        <v>-0.19296875</v>
       </c>
       <c r="J2">
-        <v>-0.1224</v>
+        <v>-0.19296875</v>
       </c>
       <c r="K2">
-        <v>-0.92</v>
+        <v>-2.44</v>
       </c>
       <c r="L2">
-        <v>-0.0736</v>
+        <v>-0.190625</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.63</v>
+        <v>5.05</v>
       </c>
       <c r="V2">
-        <v>0.1640860215053764</v>
+        <v>0.2837078651685393</v>
       </c>
       <c r="W2">
-        <v>-0.07540983606557378</v>
+        <v>-0.2140350877192982</v>
       </c>
       <c r="X2">
-        <v>0.1017454751891429</v>
+        <v>0.08740049431782457</v>
       </c>
       <c r="Y2">
-        <v>-0.1771553112547167</v>
+        <v>-0.3014355820371228</v>
       </c>
       <c r="Z2">
-        <v>1.414027149321267</v>
+        <v>1.31958762886598</v>
       </c>
       <c r="AA2">
-        <v>-0.1730769230769231</v>
+        <v>-0.254639175257732</v>
       </c>
       <c r="AB2">
-        <v>0.09697737829662524</v>
+        <v>0.08027707203900188</v>
       </c>
       <c r="AC2">
-        <v>-0.2700543013735483</v>
+        <v>-0.3349162472967339</v>
       </c>
       <c r="AD2">
-        <v>6.4</v>
+        <v>6.27</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.4</v>
+        <v>6.27</v>
       </c>
       <c r="AG2">
-        <v>-1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH2">
-        <v>0.1209829867674858</v>
+        <v>0.2604902368093062</v>
       </c>
       <c r="AI2">
-        <v>0.3516483516483516</v>
+        <v>0.3887166769993801</v>
       </c>
       <c r="AJ2">
-        <v>-0.02717031146454605</v>
+        <v>0.06414300736067297</v>
       </c>
       <c r="AK2">
-        <v>-0.1163670766319772</v>
+        <v>0.1101083032490975</v>
       </c>
       <c r="AL2">
-        <v>0.111</v>
+        <v>0.243</v>
       </c>
       <c r="AM2">
-        <v>0.101</v>
+        <v>0.209</v>
       </c>
       <c r="AN2">
-        <v>-9.155937052932762</v>
+        <v>-4.976190476190475</v>
       </c>
       <c r="AO2">
-        <v>-13.78378378378378</v>
+        <v>-10.16460905349794</v>
       </c>
       <c r="AP2">
-        <v>1.759656652360514</v>
+        <v>-0.968253968253968</v>
       </c>
       <c r="AQ2">
-        <v>-15.14851485148515</v>
+        <v>-11.81818181818182</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0243</v>
+        <v>-0.0309</v>
       </c>
       <c r="G3">
-        <v>-0.24456</v>
+        <v>-0.0146875</v>
       </c>
       <c r="H3">
-        <v>-0.2472</v>
+        <v>-0.016015625</v>
       </c>
       <c r="I3">
-        <v>-0.1224</v>
+        <v>-0.19296875</v>
       </c>
       <c r="J3">
-        <v>-0.1224</v>
+        <v>-0.19296875</v>
       </c>
       <c r="K3">
-        <v>-0.92</v>
+        <v>-2.44</v>
       </c>
       <c r="L3">
-        <v>-0.0736</v>
+        <v>-0.190625</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.63</v>
+        <v>5.05</v>
       </c>
       <c r="V3">
-        <v>0.1640860215053764</v>
+        <v>0.2837078651685393</v>
       </c>
       <c r="W3">
-        <v>-0.07540983606557378</v>
+        <v>-0.2140350877192982</v>
       </c>
       <c r="X3">
-        <v>0.1017454751891429</v>
+        <v>0.08740049431782457</v>
       </c>
       <c r="Y3">
-        <v>-0.1771553112547167</v>
+        <v>-0.3014355820371228</v>
       </c>
       <c r="Z3">
-        <v>1.414027149321267</v>
+        <v>1.31958762886598</v>
       </c>
       <c r="AA3">
-        <v>-0.1730769230769231</v>
+        <v>-0.254639175257732</v>
       </c>
       <c r="AB3">
-        <v>0.09697737829662524</v>
+        <v>0.08027707203900188</v>
       </c>
       <c r="AC3">
-        <v>-0.2700543013735483</v>
+        <v>-0.3349162472967339</v>
       </c>
       <c r="AD3">
-        <v>6.4</v>
+        <v>6.27</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.4</v>
+        <v>6.27</v>
       </c>
       <c r="AG3">
-        <v>-1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH3">
-        <v>0.1209829867674858</v>
+        <v>0.2604902368093062</v>
       </c>
       <c r="AI3">
-        <v>0.3516483516483516</v>
+        <v>0.3887166769993801</v>
       </c>
       <c r="AJ3">
-        <v>-0.02717031146454605</v>
+        <v>0.06414300736067297</v>
       </c>
       <c r="AK3">
-        <v>-0.1163670766319772</v>
+        <v>0.1101083032490975</v>
       </c>
       <c r="AL3">
-        <v>0.111</v>
+        <v>0.243</v>
       </c>
       <c r="AM3">
-        <v>0.101</v>
+        <v>0.209</v>
       </c>
       <c r="AN3">
-        <v>-9.155937052932762</v>
+        <v>-4.976190476190475</v>
       </c>
       <c r="AO3">
-        <v>-13.78378378378378</v>
+        <v>-10.16460905349794</v>
       </c>
       <c r="AP3">
-        <v>1.759656652360514</v>
+        <v>-0.968253968253968</v>
       </c>
       <c r="AQ3">
-        <v>-15.14851485148515</v>
+        <v>-11.81818181818182</v>
       </c>
     </row>
   </sheetData>
